--- a/Results/Ethylene/ethylene climate change remind breakdown results.xlsx
+++ b/Results/Ethylene/ethylene climate change remind breakdown results.xlsx
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.24703018971333</v>
+        <v>2.247030189713331</v>
       </c>
       <c r="E2" t="n">
         <v>2.05956682860994</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05830763538947142</v>
+        <v>0.05830763538947138</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007128465430838359</v>
+        <v>0.007128465430838326</v>
       </c>
       <c r="H2" t="n">
-        <v>5.866487125566526e-05</v>
+        <v>5.866487125566532e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009685496893027355</v>
+        <v>0.0009685496893027323</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1210000457225222</v>
+        <v>0.1210000457225227</v>
       </c>
     </row>
     <row r="3">
@@ -529,25 +529,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.195474668305757</v>
+        <v>2.195474668305758</v>
       </c>
       <c r="E3" t="n">
-        <v>2.02823977831138</v>
+        <v>2.028239778311383</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03826073955890916</v>
+        <v>0.03826073955890928</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00702509580646017</v>
+        <v>0.007025095806460175</v>
       </c>
       <c r="H3" t="n">
         <v>5.509282240479243e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008939176858550095</v>
+        <v>0.0008939176858550105</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1210000441207484</v>
+        <v>0.1210000441207462</v>
       </c>
     </row>
     <row r="4">
@@ -565,25 +565,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.168099594630087</v>
+        <v>2.168099594630086</v>
       </c>
       <c r="E4" t="n">
         <v>2.015090205496139</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02415985234409427</v>
+        <v>0.02415985234409434</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006957453067484794</v>
+        <v>0.006957453067484799</v>
       </c>
       <c r="H4" t="n">
-        <v>5.245250383601597e-05</v>
+        <v>5.245250383601599e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008395880361606187</v>
+        <v>0.0008395880361606152</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1210000431823723</v>
+        <v>0.1210000431823715</v>
       </c>
     </row>
     <row r="5">
@@ -601,22 +601,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.155038873236965</v>
+        <v>2.155038873236966</v>
       </c>
       <c r="E5" t="n">
-        <v>1.989583746663199</v>
+        <v>1.9895837466632</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03652937388892503</v>
+        <v>0.03652937388892501</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006993094046347915</v>
+        <v>0.006993094046347919</v>
       </c>
       <c r="H5" t="n">
-        <v>5.428582416396422e-05</v>
+        <v>5.428582416396421e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000878329594269801</v>
+        <v>0.0008783295942698014</v>
       </c>
       <c r="J5" t="n">
         <v>0.1210000432200591</v>
@@ -637,25 +637,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.054352842252477</v>
+        <v>2.054352842252475</v>
       </c>
       <c r="E6" t="n">
         <v>1.918145060046607</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00757869658546944</v>
+        <v>0.007578696585469447</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006824709545031189</v>
+        <v>0.006824709545031239</v>
       </c>
       <c r="H6" t="n">
-        <v>4.969120649824881e-05</v>
+        <v>4.969120649824874e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007546445178617937</v>
+        <v>0.0007546445178617939</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1210000403510094</v>
+        <v>0.1210000403510072</v>
       </c>
     </row>
     <row r="7">
@@ -673,25 +673,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.031359031232255</v>
+        <v>2.031359031232258</v>
       </c>
       <c r="E7" t="n">
-        <v>1.899775949305172</v>
+        <v>1.899775949305173</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003050040020917564</v>
+        <v>0.003050040020917606</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006779503819872863</v>
+        <v>0.006779503819872859</v>
       </c>
       <c r="H7" t="n">
-        <v>4.839852813696656e-05</v>
+        <v>4.839852813696651e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00070509980933089</v>
+        <v>0.0007050998093308899</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1210000397488242</v>
+        <v>0.1210000397488267</v>
       </c>
     </row>
     <row r="8">
@@ -709,25 +709,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.06691095797676</v>
+        <v>2.066910957976777</v>
       </c>
       <c r="E8" t="n">
-        <v>1.920715287141168</v>
+        <v>1.920715287141167</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01745570811511387</v>
+        <v>0.01745570811511388</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006882927343856531</v>
+        <v>0.006882927343856526</v>
       </c>
       <c r="H8" t="n">
-        <v>5.132732849762768e-05</v>
+        <v>5.132732849762775e-05</v>
       </c>
       <c r="I8" t="n">
         <v>0.0008056671802477881</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1210000408678766</v>
+        <v>0.1210000408678942</v>
       </c>
     </row>
     <row r="9">
@@ -745,25 +745,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.952393673777927</v>
+        <v>1.952393673777925</v>
       </c>
       <c r="E9" t="n">
-        <v>1.821827645307025</v>
+        <v>1.821827645307023</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002058856330769774</v>
+        <v>0.002058856330769649</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006751075263008387</v>
+        <v>0.006751075263008325</v>
       </c>
       <c r="H9" t="n">
-        <v>4.816708732452677e-05</v>
+        <v>4.816708732452666e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0007078917395895204</v>
+        <v>0.0007078917395895165</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1210000380502092</v>
+        <v>0.1210000380502096</v>
       </c>
     </row>
     <row r="10">
@@ -781,25 +781,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.915602694344806</v>
+        <v>1.915602694344805</v>
       </c>
       <c r="E10" t="n">
-        <v>1.786024705077899</v>
+        <v>1.786024705077898</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001219517960998574</v>
+        <v>0.001219517960998576</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006653351408398758</v>
+        <v>0.00665335140839876</v>
       </c>
       <c r="H10" t="n">
-        <v>4.704079839672872e-05</v>
+        <v>4.704079839672871e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.000658041848202491</v>
+        <v>0.0006580418482024905</v>
       </c>
       <c r="J10" t="n">
-        <v>0.121000037250911</v>
+        <v>0.1210000372509101</v>
       </c>
     </row>
   </sheetData>
@@ -884,19 +884,19 @@
         <v>1.298055336620543</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05830763538947142</v>
+        <v>0.05830763538947138</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007128465430838359</v>
+        <v>0.007128465430838326</v>
       </c>
       <c r="H2" t="n">
-        <v>5.866487125566526e-05</v>
+        <v>5.866487125566532e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009685496893027355</v>
+        <v>0.0009685496893027323</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1210000295775853</v>
+        <v>0.1210000295775844</v>
       </c>
     </row>
     <row r="3">
@@ -914,25 +914,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.384971896860607</v>
+        <v>1.384971896860606</v>
       </c>
       <c r="E3" t="n">
-        <v>1.217737024049837</v>
+        <v>1.217737024049839</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03826073955890916</v>
+        <v>0.03826073955890928</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00702509580646017</v>
+        <v>0.007025095806460175</v>
       </c>
       <c r="H3" t="n">
         <v>5.509282240479243e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008939176858550095</v>
+        <v>0.0008939176858550105</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1210000269371401</v>
+        <v>0.1210000269371381</v>
       </c>
     </row>
     <row r="4">
@@ -956,19 +956,19 @@
         <v>1.170509908352533</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02415985234409427</v>
+        <v>0.02415985234409434</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006957453067484794</v>
+        <v>0.006957453067484799</v>
       </c>
       <c r="H4" t="n">
-        <v>5.245250383601597e-05</v>
+        <v>5.245250383601599e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008395880361606187</v>
+        <v>0.0008395880361606152</v>
       </c>
       <c r="J4" t="n">
-        <v>0.121000025276276</v>
+        <v>0.1210000252762753</v>
       </c>
     </row>
     <row r="5">
@@ -986,25 +986,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.337918605945183</v>
+        <v>1.337918605945182</v>
       </c>
       <c r="E5" t="n">
         <v>1.172463496695326</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03652937388892503</v>
+        <v>0.03652937388892501</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006993094046347915</v>
+        <v>0.006993094046347919</v>
       </c>
       <c r="H5" t="n">
-        <v>5.428582416396422e-05</v>
+        <v>5.428582416396421e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000878329594269801</v>
+        <v>0.0008783295942698014</v>
       </c>
       <c r="J5" t="n">
-        <v>0.121000025896151</v>
+        <v>0.1210000258961503</v>
       </c>
     </row>
     <row r="6">
@@ -1025,22 +1025,22 @@
         <v>1.16309929732899</v>
       </c>
       <c r="E6" t="n">
-        <v>1.026891534018746</v>
+        <v>1.026891534018745</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00757869658546944</v>
+        <v>0.007578696585469447</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006824709545031189</v>
+        <v>0.006824709545031239</v>
       </c>
       <c r="H6" t="n">
-        <v>4.969120649824881e-05</v>
+        <v>4.969120649824874e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007546445178617937</v>
+        <v>0.0007546445178617939</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1210000214553841</v>
+        <v>0.1210000214553835</v>
       </c>
     </row>
     <row r="7">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.127925167913043</v>
+        <v>1.127925167913041</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9963421051398216</v>
+        <v>0.996342105139822</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003050040020917564</v>
+        <v>0.003050040020917606</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006779503819872863</v>
+        <v>0.006779503819872859</v>
       </c>
       <c r="H7" t="n">
-        <v>4.839852813696656e-05</v>
+        <v>4.839852813696651e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00070509980933089</v>
+        <v>0.0007050998093308899</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1210000205949633</v>
+        <v>0.1210000205949604</v>
       </c>
     </row>
     <row r="8">
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.196212388673253</v>
+        <v>1.196212388673254</v>
       </c>
       <c r="E8" t="n">
-        <v>1.05001673629749</v>
+        <v>1.050016736297491</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01745570811511387</v>
+        <v>0.01745570811511388</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006882927343856531</v>
+        <v>0.006882927343856526</v>
       </c>
       <c r="H8" t="n">
-        <v>5.132732849762768e-05</v>
+        <v>5.132732849762775e-05</v>
       </c>
       <c r="I8" t="n">
         <v>0.0008056671802477881</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1210000224080474</v>
+        <v>0.1210000224080467</v>
       </c>
     </row>
     <row r="9">
@@ -1130,25 +1130,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.040555041159988</v>
+        <v>1.040555041159987</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9099890320211376</v>
+        <v>0.909989032021136</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002058856330769774</v>
+        <v>0.002058856330769649</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006751075263008387</v>
+        <v>0.006751075263008325</v>
       </c>
       <c r="H9" t="n">
-        <v>4.816708732452677e-05</v>
+        <v>4.816708732452666e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0007078917395895204</v>
+        <v>0.0007078917395895165</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1210000187181578</v>
+        <v>0.1210000187181588</v>
       </c>
     </row>
     <row r="10">
@@ -1166,25 +1166,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.028485913230056</v>
+        <v>1.028485913230054</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8989079427710714</v>
+        <v>0.8989079427710709</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001219517960998574</v>
+        <v>0.001219517960998576</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006653351408398758</v>
+        <v>0.00665335140839876</v>
       </c>
       <c r="H10" t="n">
-        <v>4.704079839672872e-05</v>
+        <v>4.704079839672871e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.000658041848202491</v>
+        <v>0.0006580418482024905</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1210000184429884</v>
+        <v>0.1210000184429865</v>
       </c>
     </row>
   </sheetData>
@@ -1263,25 +1263,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-2.379753998881966</v>
+        <v>-2.379753998881901</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.567217261891986</v>
+        <v>-2.567217261892</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05830763538947142</v>
+        <v>0.05830763538947138</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007128465430838359</v>
+        <v>0.007128465430838326</v>
       </c>
       <c r="H2" t="n">
-        <v>5.866487125566526e-05</v>
+        <v>5.866487125566532e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009685496893027355</v>
+        <v>0.0009685496893027323</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1209999476291514</v>
+        <v>0.1209999476292314</v>
       </c>
     </row>
     <row r="3">
@@ -1299,25 +1299,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-2.664639198425407</v>
+        <v>-2.664639198425443</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.83187398537966</v>
+        <v>-2.831873985379704</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03826073955890916</v>
+        <v>0.03826073955890928</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00702509580646017</v>
+        <v>0.007025095806460175</v>
       </c>
       <c r="H3" t="n">
         <v>5.509282240479243e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008939176858550095</v>
+        <v>0.0008939176858550105</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1209999410806248</v>
+        <v>0.1209999410806319</v>
       </c>
     </row>
     <row r="4">
@@ -1335,25 +1335,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-2.844545543944661</v>
+        <v>-2.844545543944586</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.997554826804643</v>
+        <v>-2.997554826804584</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02415985234409427</v>
+        <v>0.02415985234409434</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006957453067484794</v>
+        <v>0.006957453067484799</v>
       </c>
       <c r="H4" t="n">
-        <v>5.245250383601597e-05</v>
+        <v>5.245250383601599e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008395880361606187</v>
+        <v>0.0008395880361606152</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1209999369084067</v>
+        <v>0.1209999369084218</v>
       </c>
     </row>
     <row r="5">
@@ -1371,25 +1371,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-2.726108974661444</v>
+        <v>-2.726108974661453</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.891563997749148</v>
+        <v>-2.891563997749227</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03652937388892503</v>
+        <v>0.03652937388892501</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006993094046347915</v>
+        <v>0.006993094046347919</v>
       </c>
       <c r="H5" t="n">
-        <v>5.428582416396422e-05</v>
+        <v>5.428582416396421e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000878329594269801</v>
+        <v>0.0008783295942698014</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1209999397339971</v>
+        <v>0.1209999397340673</v>
       </c>
     </row>
     <row r="6">
@@ -1407,25 +1407,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-3.131842838990837</v>
+        <v>-3.131842838990868</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.268050511243155</v>
+        <v>-3.268050511243296</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00757869658546944</v>
+        <v>0.007578696585469447</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006824709545031189</v>
+        <v>0.006824709545031239</v>
       </c>
       <c r="H6" t="n">
-        <v>4.969120649824881e-05</v>
+        <v>4.969120649824874e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007546445178617937</v>
+        <v>0.0007546445178617939</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1209999303974572</v>
+        <v>0.1209999303975668</v>
       </c>
     </row>
     <row r="7">
@@ -1443,25 +1443,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-3.247910064876353</v>
+        <v>-3.247910064876401</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.379493034876722</v>
+        <v>-3.379493034876743</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003050040020917564</v>
+        <v>0.003050040020917606</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006779503819872863</v>
+        <v>0.006779503819872859</v>
       </c>
       <c r="H7" t="n">
-        <v>4.839852813696656e-05</v>
+        <v>4.839852813696651e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00070509980933089</v>
+        <v>0.0007050998093308899</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1209999278221106</v>
+        <v>0.1209999278220839</v>
       </c>
     </row>
     <row r="8">
@@ -1479,25 +1479,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-2.958659886728446</v>
+        <v>-2.958659886728345</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.104855451015909</v>
+        <v>-3.104855451015925</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01745570811511387</v>
+        <v>0.01745570811511388</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006882927343856531</v>
+        <v>0.006882927343856526</v>
       </c>
       <c r="H8" t="n">
-        <v>5.132732849762768e-05</v>
+        <v>5.132732849762775e-05</v>
       </c>
       <c r="I8" t="n">
         <v>0.0008056671802477881</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1209999343197472</v>
+        <v>0.1209999343198636</v>
       </c>
     </row>
     <row r="9">
@@ -1515,25 +1515,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-3.250597759388906</v>
+        <v>-3.250597759388941</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.381163677550255</v>
+        <v>-3.381163677550238</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002058856330769774</v>
+        <v>0.002058856330769649</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006751075263008387</v>
+        <v>0.006751075263008325</v>
       </c>
       <c r="H9" t="n">
-        <v>4.816708732452677e-05</v>
+        <v>4.816708732452666e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0007078917395895204</v>
+        <v>0.0007078917395895165</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1209999277406566</v>
+        <v>0.1209999277406055</v>
       </c>
     </row>
     <row r="10">
@@ -1551,25 +1551,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-3.350002447951357</v>
+        <v>-3.35000244795131</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.479580325581244</v>
+        <v>-3.479580325581208</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001219517960998574</v>
+        <v>0.001219517960998576</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006653351408398758</v>
+        <v>0.00665335140839876</v>
       </c>
       <c r="H10" t="n">
-        <v>4.704079839672872e-05</v>
+        <v>4.704079839672871e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.000658041848202491</v>
+        <v>0.0006580418482024905</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1209999256138907</v>
+        <v>0.1209999256139018</v>
       </c>
     </row>
   </sheetData>
@@ -1648,25 +1648,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-2.087624422205596</v>
+        <v>-2.08762442220559</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.275087691409211</v>
+        <v>-2.275087691409186</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05830763538947142</v>
+        <v>0.05830763538947138</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007128465430838359</v>
+        <v>0.007128465430838326</v>
       </c>
       <c r="H2" t="n">
-        <v>5.866487125566526e-05</v>
+        <v>5.866487125566532e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009685496893027355</v>
+        <v>0.0009685496893027323</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1209999538227469</v>
+        <v>0.1209999538227278</v>
       </c>
     </row>
     <row r="3">
@@ -1684,25 +1684,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-2.481729778920445</v>
+        <v>-2.481729778920406</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.648964569752599</v>
+        <v>-2.648964569752581</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03826073955890916</v>
+        <v>0.03826073955890928</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00702509580646017</v>
+        <v>0.007025095806460175</v>
       </c>
       <c r="H3" t="n">
         <v>5.509282240479243e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008939176858550095</v>
+        <v>0.0008939176858550105</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1209999449585251</v>
+        <v>0.1209999449585464</v>
       </c>
     </row>
     <row r="4">
@@ -1720,25 +1720,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-2.721415518028476</v>
+        <v>-2.721415518028436</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.874424803498886</v>
+        <v>-2.874424803498952</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02415985234409427</v>
+        <v>0.02415985234409434</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006957453067484794</v>
+        <v>0.006957453067484799</v>
       </c>
       <c r="H4" t="n">
-        <v>5.245250383601597e-05</v>
+        <v>5.245250383601599e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008395880361606187</v>
+        <v>0.0008395880361606152</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1209999395188346</v>
+        <v>0.1209999395189403</v>
       </c>
     </row>
     <row r="5">
@@ -1756,25 +1756,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-2.493400812952307</v>
+        <v>-2.493400812952344</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.658855840973693</v>
+        <v>-2.658855840973718</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03652937388892503</v>
+        <v>0.03652937388892501</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006993094046347915</v>
+        <v>0.006993094046347919</v>
       </c>
       <c r="H5" t="n">
-        <v>5.428582416396422e-05</v>
+        <v>5.428582416396421e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000878329594269801</v>
+        <v>0.0008783295942698014</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1209999446676795</v>
+        <v>0.1209999446676675</v>
       </c>
     </row>
     <row r="6">
@@ -1792,25 +1792,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-2.994205778363122</v>
+        <v>-2.994205778363167</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.130413453533634</v>
+        <v>-3.130413453533676</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00757869658546944</v>
+        <v>0.007578696585469447</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006824709545031189</v>
+        <v>0.006824709545031239</v>
       </c>
       <c r="H6" t="n">
-        <v>4.969120649824881e-05</v>
+        <v>4.969120649824874e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007546445178617937</v>
+        <v>0.0007546445178617939</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1209999333156504</v>
+        <v>0.1209999333156486</v>
       </c>
     </row>
     <row r="7">
@@ -1828,25 +1828,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-3.123664279726228</v>
+        <v>-3.123664279726205</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.255247252360747</v>
+        <v>-3.255247252360766</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003050040020917564</v>
+        <v>0.003050040020917606</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006779503819872863</v>
+        <v>0.006779503819872859</v>
       </c>
       <c r="H7" t="n">
-        <v>4.839852813696656e-05</v>
+        <v>4.839852813696651e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00070509980933089</v>
+        <v>0.0007050998093308899</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1209999304562612</v>
+        <v>0.120999930456303</v>
       </c>
     </row>
     <row r="8">
@@ -1864,25 +1864,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-2.769349887005661</v>
+        <v>-2.769349887005657</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.915545455306852</v>
+        <v>-2.915545455306827</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01745570811511387</v>
+        <v>0.01745570811511388</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006882927343856531</v>
+        <v>0.006882927343856526</v>
       </c>
       <c r="H8" t="n">
-        <v>5.132732849762768e-05</v>
+        <v>5.132732849762775e-05</v>
       </c>
       <c r="I8" t="n">
         <v>0.0008056671802477881</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1209999383334748</v>
+        <v>0.1209999383334543</v>
       </c>
     </row>
     <row r="9">
@@ -1900,25 +1900,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-3.109130123917837</v>
+        <v>-3.109130123917923</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.239696045078487</v>
+        <v>-3.239696045078501</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002058856330769774</v>
+        <v>0.002058856330769649</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006751075263008387</v>
+        <v>0.006751075263008325</v>
       </c>
       <c r="H9" t="n">
-        <v>4.816708732452677e-05</v>
+        <v>4.816708732452666e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0007078917395895204</v>
+        <v>0.0007078917395895165</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1209999307399574</v>
+        <v>0.1209999307398864</v>
       </c>
     </row>
     <row r="10">
@@ -1936,25 +1936,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-3.208264884856745</v>
+        <v>-3.208264884856727</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.337842765491642</v>
+        <v>-3.337842765491601</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001219517960998574</v>
+        <v>0.001219517960998576</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006653351408398758</v>
+        <v>0.00665335140839876</v>
       </c>
       <c r="H10" t="n">
-        <v>4.704079839672872e-05</v>
+        <v>4.704079839672871e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.000658041848202491</v>
+        <v>0.0006580418482024905</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1209999286189012</v>
+        <v>0.1209999286188772</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ethylene/ethylene climate change remind breakdown results.xlsx
+++ b/Results/Ethylene/ethylene climate change remind breakdown results.xlsx
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.247030189713331</v>
+        <v>2.24703018971333</v>
       </c>
       <c r="E2" t="n">
         <v>2.05956682860994</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05830763538947138</v>
+        <v>0.05830763538947147</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007128465430838326</v>
+        <v>0.007128465430838368</v>
       </c>
       <c r="H2" t="n">
-        <v>5.866487125566532e-05</v>
+        <v>5.866487125566537e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009685496893027323</v>
+        <v>0.0009685496893027317</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1210000457225227</v>
+        <v>0.1210000457225222</v>
       </c>
     </row>
     <row r="3">
@@ -532,22 +532,22 @@
         <v>2.195474668305758</v>
       </c>
       <c r="E3" t="n">
-        <v>2.028239778311383</v>
+        <v>2.028239778311381</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03826073955890928</v>
+        <v>0.03826073955890908</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007025095806460175</v>
+        <v>0.00702509580646017</v>
       </c>
       <c r="H3" t="n">
-        <v>5.509282240479243e-05</v>
+        <v>5.509282240479241e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008939176858550105</v>
+        <v>0.0008939176858550121</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1210000441207462</v>
+        <v>0.1210000441207479</v>
       </c>
     </row>
     <row r="4">
@@ -565,25 +565,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.168099594630086</v>
+        <v>2.168099594630085</v>
       </c>
       <c r="E4" t="n">
         <v>2.015090205496139</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02415985234409434</v>
+        <v>0.02415985234409436</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006957453067484799</v>
+        <v>0.006957453067484792</v>
       </c>
       <c r="H4" t="n">
         <v>5.245250383601599e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008395880361606152</v>
+        <v>0.0008395880361606199</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1210000431823715</v>
+        <v>0.1210000431823706</v>
       </c>
     </row>
     <row r="5">
@@ -601,25 +601,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.155038873236966</v>
+        <v>2.155038873236967</v>
       </c>
       <c r="E5" t="n">
         <v>1.9895837466632</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03652937388892501</v>
+        <v>0.03652937388892507</v>
       </c>
       <c r="G5" t="n">
         <v>0.006993094046347919</v>
       </c>
       <c r="H5" t="n">
-        <v>5.428582416396421e-05</v>
+        <v>5.428582416396427e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0008783295942698014</v>
+        <v>0.0008783295942698025</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1210000432200591</v>
+        <v>0.1210000432200609</v>
       </c>
     </row>
     <row r="6">
@@ -637,25 +637,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.054352842252475</v>
+        <v>2.054352842252476</v>
       </c>
       <c r="E6" t="n">
-        <v>1.918145060046607</v>
+        <v>1.918145060046606</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007578696585469447</v>
+        <v>0.007578696585469449</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006824709545031239</v>
+        <v>0.006824709545031214</v>
       </c>
       <c r="H6" t="n">
-        <v>4.969120649824874e-05</v>
+        <v>4.969120649824873e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007546445178617939</v>
+        <v>0.0007546445178617898</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1210000403510072</v>
+        <v>0.121000040351009</v>
       </c>
     </row>
     <row r="7">
@@ -673,25 +673,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.031359031232258</v>
+        <v>2.031359031232256</v>
       </c>
       <c r="E7" t="n">
-        <v>1.899775949305173</v>
+        <v>1.899775949305174</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003050040020917606</v>
+        <v>0.003050040020917633</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006779503819872859</v>
+        <v>0.006779503819872852</v>
       </c>
       <c r="H7" t="n">
-        <v>4.839852813696651e-05</v>
+        <v>4.839852813696652e-05</v>
       </c>
       <c r="I7" t="n">
         <v>0.0007050998093308899</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1210000397488267</v>
+        <v>0.1210000397488236</v>
       </c>
     </row>
     <row r="8">
@@ -709,25 +709,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.066910957976777</v>
+        <v>2.06691095797676</v>
       </c>
       <c r="E8" t="n">
         <v>1.920715287141167</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01745570811511388</v>
+        <v>0.01745570811511387</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006882927343856526</v>
+        <v>0.006882927343856522</v>
       </c>
       <c r="H8" t="n">
-        <v>5.132732849762775e-05</v>
+        <v>5.132732849762774e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008056671802477881</v>
+        <v>0.0008056671802477867</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1210000408678942</v>
+        <v>0.1210000408678771</v>
       </c>
     </row>
     <row r="9">
@@ -745,25 +745,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.952393673777925</v>
+        <v>1.952393673777924</v>
       </c>
       <c r="E9" t="n">
-        <v>1.821827645307023</v>
+        <v>1.821827645307024</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002058856330769649</v>
+        <v>0.002058856330769752</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006751075263008325</v>
+        <v>0.006751075263008391</v>
       </c>
       <c r="H9" t="n">
-        <v>4.816708732452666e-05</v>
+        <v>4.816708732452671e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0007078917395895165</v>
+        <v>0.0007078917395895196</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1210000380502096</v>
+        <v>0.1210000380502085</v>
       </c>
     </row>
     <row r="10">
@@ -781,25 +781,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.915602694344805</v>
+        <v>1.915602694344808</v>
       </c>
       <c r="E10" t="n">
-        <v>1.786024705077898</v>
+        <v>1.7860247050779</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001219517960998576</v>
+        <v>0.001219517960998591</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00665335140839876</v>
+        <v>0.006653351408398759</v>
       </c>
       <c r="H10" t="n">
-        <v>4.704079839672871e-05</v>
+        <v>4.704079839672872e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0006580418482024905</v>
+        <v>0.0006580418482024903</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1210000372509101</v>
+        <v>0.1210000372509106</v>
       </c>
     </row>
   </sheetData>
@@ -878,25 +878,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.485518681578996</v>
+        <v>1.485518681578997</v>
       </c>
       <c r="E2" t="n">
         <v>1.298055336620543</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05830763538947138</v>
+        <v>0.05830763538947147</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007128465430838326</v>
+        <v>0.007128465430838368</v>
       </c>
       <c r="H2" t="n">
-        <v>5.866487125566532e-05</v>
+        <v>5.866487125566537e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009685496893027323</v>
+        <v>0.0009685496893027317</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1210000295775844</v>
+        <v>0.1210000295775857</v>
       </c>
     </row>
     <row r="3">
@@ -914,25 +914,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.384971896860606</v>
+        <v>1.384971896860607</v>
       </c>
       <c r="E3" t="n">
         <v>1.217737024049839</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03826073955890928</v>
+        <v>0.03826073955890908</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007025095806460175</v>
+        <v>0.00702509580646017</v>
       </c>
       <c r="H3" t="n">
-        <v>5.509282240479243e-05</v>
+        <v>5.509282240479241e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008939176858550105</v>
+        <v>0.0008939176858550121</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1210000269371381</v>
+        <v>0.1210000269371387</v>
       </c>
     </row>
     <row r="4">
@@ -953,19 +953,19 @@
         <v>1.323519279580385</v>
       </c>
       <c r="E4" t="n">
-        <v>1.170509908352533</v>
+        <v>1.170509908352534</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02415985234409434</v>
+        <v>0.02415985234409436</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006957453067484799</v>
+        <v>0.006957453067484792</v>
       </c>
       <c r="H4" t="n">
         <v>5.245250383601599e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008395880361606152</v>
+        <v>0.0008395880361606199</v>
       </c>
       <c r="J4" t="n">
         <v>0.1210000252762753</v>
@@ -986,25 +986,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.337918605945182</v>
+        <v>1.337918605945184</v>
       </c>
       <c r="E5" t="n">
-        <v>1.172463496695326</v>
+        <v>1.172463496695327</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03652937388892501</v>
+        <v>0.03652937388892507</v>
       </c>
       <c r="G5" t="n">
         <v>0.006993094046347919</v>
       </c>
       <c r="H5" t="n">
-        <v>5.428582416396421e-05</v>
+        <v>5.428582416396427e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0008783295942698014</v>
+        <v>0.0008783295942698025</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1210000258961503</v>
+        <v>0.121000025896151</v>
       </c>
     </row>
     <row r="6">
@@ -1028,19 +1028,19 @@
         <v>1.026891534018745</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007578696585469447</v>
+        <v>0.007578696585469449</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006824709545031239</v>
+        <v>0.006824709545031214</v>
       </c>
       <c r="H6" t="n">
-        <v>4.969120649824874e-05</v>
+        <v>4.969120649824873e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007546445178617939</v>
+        <v>0.0007546445178617898</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1210000214553835</v>
+        <v>0.1210000214553841</v>
       </c>
     </row>
     <row r="7">
@@ -1058,25 +1058,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.127925167913041</v>
+        <v>1.127925167913044</v>
       </c>
       <c r="E7" t="n">
         <v>0.996342105139822</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003050040020917606</v>
+        <v>0.003050040020917633</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006779503819872859</v>
+        <v>0.006779503819872852</v>
       </c>
       <c r="H7" t="n">
-        <v>4.839852813696651e-05</v>
+        <v>4.839852813696652e-05</v>
       </c>
       <c r="I7" t="n">
         <v>0.0007050998093308899</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1210000205949604</v>
+        <v>0.1210000205949637</v>
       </c>
     </row>
     <row r="8">
@@ -1100,19 +1100,19 @@
         <v>1.050016736297491</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01745570811511388</v>
+        <v>0.01745570811511387</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006882927343856526</v>
+        <v>0.006882927343856522</v>
       </c>
       <c r="H8" t="n">
-        <v>5.132732849762775e-05</v>
+        <v>5.132732849762774e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008056671802477881</v>
+        <v>0.0008056671802477867</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1210000224080467</v>
+        <v>0.1210000224080465</v>
       </c>
     </row>
     <row r="9">
@@ -1133,22 +1133,22 @@
         <v>1.040555041159987</v>
       </c>
       <c r="E9" t="n">
-        <v>0.909989032021136</v>
+        <v>0.9099890320211373</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002058856330769649</v>
+        <v>0.002058856330769752</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006751075263008325</v>
+        <v>0.006751075263008391</v>
       </c>
       <c r="H9" t="n">
-        <v>4.816708732452666e-05</v>
+        <v>4.816708732452671e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0007078917395895165</v>
+        <v>0.0007078917395895196</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1210000187181588</v>
+        <v>0.1210000187181577</v>
       </c>
     </row>
     <row r="10">
@@ -1166,25 +1166,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.028485913230054</v>
+        <v>1.028485913230057</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8989079427710709</v>
+        <v>0.8989079427710718</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001219517960998576</v>
+        <v>0.001219517960998591</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00665335140839876</v>
+        <v>0.006653351408398759</v>
       </c>
       <c r="H10" t="n">
-        <v>4.704079839672871e-05</v>
+        <v>4.704079839672872e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0006580418482024905</v>
+        <v>0.0006580418482024903</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1210000184429865</v>
+        <v>0.1210000184429882</v>
       </c>
     </row>
   </sheetData>
@@ -1263,25 +1263,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-2.379753998881901</v>
+        <v>-2.379753998881928</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.567217261892</v>
+        <v>-2.56721726189204</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05830763538947138</v>
+        <v>0.05830763538947147</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007128465430838326</v>
+        <v>0.007128465430838368</v>
       </c>
       <c r="H2" t="n">
-        <v>5.866487125566532e-05</v>
+        <v>5.866487125566537e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009685496893027323</v>
+        <v>0.0009685496893027317</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1209999476292314</v>
+        <v>0.1209999476292434</v>
       </c>
     </row>
     <row r="3">
@@ -1299,25 +1299,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-2.664639198425443</v>
+        <v>-2.664639198425323</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.831873985379704</v>
+        <v>-2.831873985379497</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03826073955890928</v>
+        <v>0.03826073955890908</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007025095806460175</v>
+        <v>0.00702509580646017</v>
       </c>
       <c r="H3" t="n">
-        <v>5.509282240479243e-05</v>
+        <v>5.509282240479241e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008939176858550105</v>
+        <v>0.0008939176858550121</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1209999410806319</v>
+        <v>0.1209999410805449</v>
       </c>
     </row>
     <row r="4">
@@ -1335,25 +1335,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-2.844545543944586</v>
+        <v>-2.844545543944604</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.997554826804584</v>
+        <v>-2.997554826804676</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02415985234409434</v>
+        <v>0.02415985234409436</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006957453067484799</v>
+        <v>0.006957453067484792</v>
       </c>
       <c r="H4" t="n">
         <v>5.245250383601599e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008395880361606152</v>
+        <v>0.0008395880361606199</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1209999369084218</v>
+        <v>0.1209999369084964</v>
       </c>
     </row>
     <row r="5">
@@ -1371,25 +1371,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-2.726108974661453</v>
+        <v>-2.726108974661535</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.891563997749227</v>
+        <v>-2.891563997749128</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03652937388892501</v>
+        <v>0.03652937388892507</v>
       </c>
       <c r="G5" t="n">
         <v>0.006993094046347919</v>
       </c>
       <c r="H5" t="n">
-        <v>5.428582416396421e-05</v>
+        <v>5.428582416396427e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0008783295942698014</v>
+        <v>0.0008783295942698025</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1209999397340673</v>
+        <v>0.1209999397338857</v>
       </c>
     </row>
     <row r="6">
@@ -1407,25 +1407,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-3.131842838990868</v>
+        <v>-3.131842838990788</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.268050511243296</v>
+        <v>-3.268050511243299</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007578696585469447</v>
+        <v>0.007578696585469449</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006824709545031239</v>
+        <v>0.006824709545031214</v>
       </c>
       <c r="H6" t="n">
-        <v>4.969120649824874e-05</v>
+        <v>4.969120649824873e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007546445178617939</v>
+        <v>0.0007546445178617898</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1209999303975668</v>
+        <v>0.1209999303976503</v>
       </c>
     </row>
     <row r="7">
@@ -1443,25 +1443,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-3.247910064876401</v>
+        <v>-3.247910064876312</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.379493034876743</v>
+        <v>-3.379493034876733</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003050040020917606</v>
+        <v>0.003050040020917633</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006779503819872859</v>
+        <v>0.006779503819872852</v>
       </c>
       <c r="H7" t="n">
-        <v>4.839852813696651e-05</v>
+        <v>4.839852813696652e-05</v>
       </c>
       <c r="I7" t="n">
         <v>0.0007050998093308899</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1209999278220839</v>
+        <v>0.1209999278221625</v>
       </c>
     </row>
     <row r="8">
@@ -1479,25 +1479,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-2.958659886728345</v>
+        <v>-2.958659886728314</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.104855451015925</v>
+        <v>-3.104855451015982</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01745570811511388</v>
+        <v>0.01745570811511387</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006882927343856526</v>
+        <v>0.006882927343856522</v>
       </c>
       <c r="H8" t="n">
-        <v>5.132732849762775e-05</v>
+        <v>5.132732849762774e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008056671802477881</v>
+        <v>0.0008056671802477867</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1209999343198636</v>
+        <v>0.1209999343199524</v>
       </c>
     </row>
     <row r="9">
@@ -1515,25 +1515,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-3.250597759388941</v>
+        <v>-3.250597759388933</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.381163677550238</v>
+        <v>-3.381163677550268</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002058856330769649</v>
+        <v>0.002058856330769752</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006751075263008325</v>
+        <v>0.006751075263008391</v>
       </c>
       <c r="H9" t="n">
-        <v>4.816708732452666e-05</v>
+        <v>4.816708732452671e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0007078917395895165</v>
+        <v>0.0007078917395895196</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1209999277406055</v>
+        <v>0.1209999277406433</v>
       </c>
     </row>
     <row r="10">
@@ -1551,25 +1551,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-3.35000244795131</v>
+        <v>-3.350002447951376</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.479580325581208</v>
+        <v>-3.479580325581214</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001219517960998576</v>
+        <v>0.001219517960998591</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00665335140839876</v>
+        <v>0.006653351408398759</v>
       </c>
       <c r="H10" t="n">
-        <v>4.704079839672871e-05</v>
+        <v>4.704079839672872e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0006580418482024905</v>
+        <v>0.0006580418482024903</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1209999256139018</v>
+        <v>0.1209999256138419</v>
       </c>
     </row>
   </sheetData>
@@ -1648,25 +1648,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-2.08762442220559</v>
+        <v>-2.087624422205642</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.275087691409186</v>
+        <v>-2.275087691409169</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05830763538947138</v>
+        <v>0.05830763538947147</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007128465430838326</v>
+        <v>0.007128465430838368</v>
       </c>
       <c r="H2" t="n">
-        <v>5.866487125566532e-05</v>
+        <v>5.866487125566537e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009685496893027323</v>
+        <v>0.0009685496893027317</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1209999538227278</v>
+        <v>0.120999953822658</v>
       </c>
     </row>
     <row r="3">
@@ -1684,25 +1684,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-2.481729778920406</v>
+        <v>-2.481729778920331</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.648964569752581</v>
+        <v>-2.648964569752448</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03826073955890928</v>
+        <v>0.03826073955890908</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007025095806460175</v>
+        <v>0.00702509580646017</v>
       </c>
       <c r="H3" t="n">
-        <v>5.509282240479243e-05</v>
+        <v>5.509282240479241e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008939176858550105</v>
+        <v>0.0008939176858550121</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1209999449585464</v>
+        <v>0.1209999449584882</v>
       </c>
     </row>
     <row r="4">
@@ -1720,25 +1720,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-2.721415518028436</v>
+        <v>-2.721415518028353</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.874424803498952</v>
+        <v>-2.874424803498843</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02415985234409434</v>
+        <v>0.02415985234409436</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006957453067484799</v>
+        <v>0.006957453067484792</v>
       </c>
       <c r="H4" t="n">
         <v>5.245250383601599e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008395880361606152</v>
+        <v>0.0008395880361606199</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1209999395189403</v>
+        <v>0.1209999395189145</v>
       </c>
     </row>
     <row r="5">
@@ -1756,25 +1756,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-2.493400812952344</v>
+        <v>-2.493400812952359</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.658855840973718</v>
+        <v>-2.658855840973816</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03652937388892501</v>
+        <v>0.03652937388892507</v>
       </c>
       <c r="G5" t="n">
         <v>0.006993094046347919</v>
       </c>
       <c r="H5" t="n">
-        <v>5.428582416396421e-05</v>
+        <v>5.428582416396427e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0008783295942698014</v>
+        <v>0.0008783295942698025</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1209999446676675</v>
+        <v>0.1209999446677497</v>
       </c>
     </row>
     <row r="6">
@@ -1792,25 +1792,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-2.994205778363167</v>
+        <v>-2.994205778363217</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.130413453533676</v>
+        <v>-3.13041345353369</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007578696585469447</v>
+        <v>0.007578696585469449</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006824709545031239</v>
+        <v>0.006824709545031214</v>
       </c>
       <c r="H6" t="n">
-        <v>4.969120649824874e-05</v>
+        <v>4.969120649824873e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007546445178617939</v>
+        <v>0.0007546445178617898</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1209999333156486</v>
+        <v>0.1209999333156127</v>
       </c>
     </row>
     <row r="7">
@@ -1828,25 +1828,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-3.123664279726205</v>
+        <v>-3.123664279726118</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.255247252360766</v>
+        <v>-3.255247252360727</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003050040020917606</v>
+        <v>0.003050040020917633</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006779503819872859</v>
+        <v>0.006779503819872852</v>
       </c>
       <c r="H7" t="n">
-        <v>4.839852813696651e-05</v>
+        <v>4.839852813696652e-05</v>
       </c>
       <c r="I7" t="n">
         <v>0.0007050998093308899</v>
       </c>
       <c r="J7" t="n">
-        <v>0.120999930456303</v>
+        <v>0.12099993045635</v>
       </c>
     </row>
     <row r="8">
@@ -1864,25 +1864,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-2.769349887005657</v>
+        <v>-2.769349887005804</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.915545455306827</v>
+        <v>-2.915545455306821</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01745570811511388</v>
+        <v>0.01745570811511387</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006882927343856526</v>
+        <v>0.006882927343856522</v>
       </c>
       <c r="H8" t="n">
-        <v>5.132732849762775e-05</v>
+        <v>5.132732849762774e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0008056671802477881</v>
+        <v>0.0008056671802477867</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1209999383334543</v>
+        <v>0.1209999383333007</v>
       </c>
     </row>
     <row r="9">
@@ -1900,25 +1900,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-3.109130123917923</v>
+        <v>-3.109130123917796</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.239696045078501</v>
+        <v>-3.239696045078552</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002058856330769649</v>
+        <v>0.002058856330769752</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006751075263008325</v>
+        <v>0.006751075263008391</v>
       </c>
       <c r="H9" t="n">
-        <v>4.816708732452666e-05</v>
+        <v>4.816708732452671e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0007078917395895165</v>
+        <v>0.0007078917395895196</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1209999307398864</v>
+        <v>0.120999930740064</v>
       </c>
     </row>
     <row r="10">
@@ -1936,25 +1936,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-3.208264884856727</v>
+        <v>-3.208264884856749</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.337842765491601</v>
+        <v>-3.337842765491605</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001219517960998576</v>
+        <v>0.001219517960998591</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00665335140839876</v>
+        <v>0.006653351408398759</v>
       </c>
       <c r="H10" t="n">
-        <v>4.704079839672871e-05</v>
+        <v>4.704079839672872e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0006580418482024905</v>
+        <v>0.0006580418482024903</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1209999286188772</v>
+        <v>0.1209999286188599</v>
       </c>
     </row>
   </sheetData>
